--- a/VC-Cap-Table-Example.xlsx
+++ b/VC-Cap-Table-Example.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3989B8B-C1E4-4505-8DAD-7230A83C6DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E08247-E550-4820-BC4E-4E5FB1F906EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6228" yWindow="4440" windowWidth="30960" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example 1" sheetId="1" r:id="rId1"/>
@@ -136,15 +136,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;0&quot;M&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.0%"/>
-    <numFmt numFmtId="171" formatCode="&quot;$&quot;0.0&quot;M&quot;"/>
-    <numFmt numFmtId="172" formatCode="[$-409]mmm\-yy"/>
+    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;0&quot;M&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;0.0&quot;M&quot;"/>
+    <numFmt numFmtId="168" formatCode="[$-409]mmm\-yy"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -353,72 +353,72 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="5" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="5" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="7" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="5" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -787,15 +787,15 @@
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
       <c r="G15" s="25">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H15" s="9">
         <f t="shared" ref="H15:H23" si="0">SUM(C15:G15)</f>
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="I15" s="26">
         <f t="shared" ref="I15:I23" si="1">H15/$H$24</f>
-        <v>3.6057692307692304E-2</v>
+        <v>3.8369304556354913E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -817,7 +817,7 @@
       </c>
       <c r="I16" s="26">
         <f t="shared" si="1"/>
-        <v>6.25E-2</v>
+        <v>6.235011990407674E-2</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -839,7 +839,7 @@
       </c>
       <c r="I17" s="26">
         <f t="shared" si="1"/>
-        <v>8.8942307692307696E-2</v>
+        <v>8.8729016786570747E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -861,7 +861,7 @@
       </c>
       <c r="I18" s="26">
         <f t="shared" si="1"/>
-        <v>0.11538461538461539</v>
+        <v>0.11510791366906475</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -881,7 +881,7 @@
       </c>
       <c r="I19" s="26">
         <f t="shared" si="1"/>
-        <v>0.1201923076923077</v>
+        <v>0.11990407673860912</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -905,7 +905,7 @@
       </c>
       <c r="I20" s="26">
         <f t="shared" si="1"/>
-        <v>0.14423076923076922</v>
+        <v>0.14388489208633093</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -927,7 +927,7 @@
       </c>
       <c r="I21" s="26">
         <f t="shared" si="1"/>
-        <v>0.16826923076923078</v>
+        <v>0.16786570743405277</v>
       </c>
     </row>
     <row r="22" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -947,7 +947,7 @@
       </c>
       <c r="I22" s="26">
         <f t="shared" si="1"/>
-        <v>0.1201923076923077</v>
+        <v>0.11990407673860912</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -967,7 +967,7 @@
       </c>
       <c r="I23" s="26">
         <f t="shared" si="1"/>
-        <v>0.14423076923076922</v>
+        <v>0.14388489208633093</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -992,11 +992,11 @@
       </c>
       <c r="G24" s="30">
         <f t="shared" si="2"/>
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="H24" s="30">
         <f t="shared" si="2"/>
-        <v>41600</v>
+        <v>41700</v>
       </c>
       <c r="I24" s="31">
         <f t="shared" si="2"/>
@@ -1009,23 +1009,23 @@
       </c>
       <c r="C25" s="33">
         <f t="shared" ref="C25:H25" si="3">C24/$H$24</f>
-        <v>0.50480769230769229</v>
+        <v>0.50359712230215825</v>
       </c>
       <c r="D25" s="33">
         <f t="shared" si="3"/>
-        <v>2.403846153846154E-2</v>
+        <v>2.3980815347721823E-2</v>
       </c>
       <c r="E25" s="33">
         <f t="shared" si="3"/>
-        <v>0.1201923076923077</v>
+        <v>0.11990407673860912</v>
       </c>
       <c r="F25" s="33">
         <f t="shared" si="3"/>
-        <v>0.28846153846153844</v>
+        <v>0.28776978417266186</v>
       </c>
       <c r="G25" s="33">
         <f t="shared" si="3"/>
-        <v>6.25E-2</v>
+        <v>6.4748201438848921E-2</v>
       </c>
       <c r="H25" s="33">
         <f t="shared" si="3"/>
